--- a/data/externalStats/File1/RPT_RPT9853920998378DH_externalStats.xlsx
+++ b/data/externalStats/File1/RPT_RPT9853920998378DH_externalStats.xlsx
@@ -2104,7 +2104,7 @@
         <v>40294.15219393585</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>34.07302870312816</v>
+        <v>34.07302870312817</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>5520.587381943595</v>
+        <v>5520.587381943594</v>
       </c>
       <c r="AI28" s="56" t="n">
         <v>9.113706901155732</v>
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>1561.3728370056</v>
+        <v>1561.372837005601</v>
       </c>
       <c r="AI41" s="56" t="n">
         <v>4.341491071594501</v>
@@ -3756,7 +3756,7 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>7437.956592937452</v>
+        <v>7437.956592937451</v>
       </c>
       <c r="AH51" s="56" t="n">
         <v>13.63594514274421</v>
@@ -4322,7 +4322,7 @@
         <v>0</v>
       </c>
       <c r="N58" s="132" t="n">
-        <v>13.79044643211359</v>
+        <v>13.7904464321136</v>
       </c>
       <c r="P58" s="130" t="n">
         <v>10.2493426186892</v>
@@ -4553,13 +4553,13 @@
         <v>166</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>74.88002245149934</v>
+        <v>74.88002245149937</v>
       </c>
       <c r="K61" s="131" t="n">
         <v>53.80356729336189</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>33.06110095461911</v>
+        <v>33.06110095461912</v>
       </c>
       <c r="M61" s="131" t="n">
         <v>1.218010259491261</v>
@@ -4568,7 +4568,7 @@
         <v>162.9627009589716</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>75.59228217781634</v>
+        <v>75.59228217781633</v>
       </c>
       <c r="Q61" s="131" t="n">
         <v>54.62386416537736</v>
@@ -4634,19 +4634,19 @@
         <v>74</v>
       </c>
       <c r="J62" s="130" t="n">
-        <v>0.946566785750185</v>
+        <v>0.9465667857501853</v>
       </c>
       <c r="K62" s="131" t="n">
         <v>11.36424964772467</v>
       </c>
       <c r="L62" s="131" t="n">
-        <v>57.74182120542003</v>
+        <v>57.74182120542004</v>
       </c>
       <c r="M62" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N62" s="132" t="n">
-        <v>70.05263763889488</v>
+        <v>70.05263763889489</v>
       </c>
       <c r="P62" s="130" t="n">
         <v>0.9413347756941125</v>
@@ -4715,7 +4715,7 @@
         <v>8</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>0.6454387887318376</v>
+        <v>0.6454387887317949</v>
       </c>
       <c r="K63" s="131" t="n">
         <v>0.1037014274659498</v>
@@ -4727,10 +4727,10 @@
         <v>5.123650723609178</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>5.951452166512968</v>
+        <v>5.951452166512926</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>0.5738078228343113</v>
+        <v>0.5738078228343255</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>0.08753547266331907</v>
@@ -4742,7 +4742,7 @@
         <v>4.764364896346361</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>5.50495106217225</v>
+        <v>5.504951062172264</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>0.5642210685925164</v>
@@ -5051,13 +5051,13 @@
         <v>4.225076113212191</v>
       </c>
       <c r="L67" s="140" t="n">
-        <v>7.669521517167252</v>
+        <v>7.669521517167253</v>
       </c>
       <c r="M67" s="140" t="n">
         <v>0</v>
       </c>
       <c r="N67" s="141" t="n">
-        <v>30.74099485995321</v>
+        <v>30.74099485995322</v>
       </c>
       <c r="P67" s="139" t="n">
         <v>21.92887624761443</v>
@@ -5066,7 +5066,7 @@
         <v>4.655064442551426</v>
       </c>
       <c r="R67" s="140" t="n">
-        <v>6.955671695501598</v>
+        <v>6.955671695501597</v>
       </c>
       <c r="S67" s="140" t="n">
         <v>0</v>
@@ -5132,7 +5132,7 @@
         <v>69.4965944817647</v>
       </c>
       <c r="L68" s="143" t="n">
-        <v>102.3374538354153</v>
+        <v>102.3374538354154</v>
       </c>
       <c r="M68" s="143" t="n">
         <v>23.44217100622897</v>
@@ -5875,7 +5875,7 @@
         <v>0</v>
       </c>
       <c r="K79" s="131" t="n">
-        <v>0.1862264093511716</v>
+        <v>0.1862264093511717</v>
       </c>
       <c r="L79" s="131" t="n">
         <v>0</v>
@@ -5914,7 +5914,7 @@
         <v>1.7498650498326</v>
       </c>
       <c r="Z79" s="132" t="n">
-        <v>5.159103848813558</v>
+        <v>5.159103848813556</v>
       </c>
     </row>
     <row r="80">
@@ -6015,10 +6015,10 @@
         <v>0</v>
       </c>
       <c r="M81" s="131" t="n">
-        <v>2.406472024668733</v>
+        <v>2.406472024668734</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>2.406472024668733</v>
+        <v>2.406472024668734</v>
       </c>
       <c r="P81" s="130" t="n">
         <v>0</v>
@@ -6381,7 +6381,7 @@
         <v>67.28893941810735</v>
       </c>
       <c r="X86" s="143" t="n">
-        <v>43.76101560028665</v>
+        <v>43.76101560028664</v>
       </c>
       <c r="Y86" s="143" t="n">
         <v>13.47010685860509</v>
@@ -6888,7 +6888,7 @@
         <v>0</v>
       </c>
       <c r="N94" s="132" t="n">
-        <v>13.79044643211359</v>
+        <v>13.7904464321136</v>
       </c>
       <c r="P94" s="130" t="n">
         <v>10.2493426186892</v>
@@ -7077,22 +7077,22 @@
         <v>166</v>
       </c>
       <c r="J97" s="130" t="n">
-        <v>74.88002245149934</v>
+        <v>74.88002245149937</v>
       </c>
       <c r="K97" s="131" t="n">
         <v>53.98979370271307</v>
       </c>
       <c r="L97" s="131" t="n">
-        <v>33.06110095461911</v>
+        <v>33.06110095461912</v>
       </c>
       <c r="M97" s="131" t="n">
         <v>2.978503417483211</v>
       </c>
       <c r="N97" s="132" t="n">
-        <v>164.9094205263147</v>
+        <v>164.9094205263148</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>75.59228217781634</v>
+        <v>75.59228217781633</v>
       </c>
       <c r="Q97" s="131" t="n">
         <v>54.80800513548264</v>
@@ -7144,19 +7144,19 @@
         <v>74</v>
       </c>
       <c r="J98" s="130" t="n">
-        <v>0.946566785750185</v>
+        <v>0.9465667857501853</v>
       </c>
       <c r="K98" s="131" t="n">
         <v>11.36424964772467</v>
       </c>
       <c r="L98" s="131" t="n">
-        <v>57.74182120542003</v>
+        <v>57.74182120542004</v>
       </c>
       <c r="M98" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N98" s="132" t="n">
-        <v>70.05263763889488</v>
+        <v>70.05263763889489</v>
       </c>
       <c r="P98" s="130" t="n">
         <v>0.9413347756941125</v>
@@ -7211,7 +7211,7 @@
         <v>8</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>0.6454387887318376</v>
+        <v>0.6454387887317949</v>
       </c>
       <c r="K99" s="131" t="n">
         <v>0.1037014274659498</v>
@@ -7223,7 +7223,7 @@
         <v>7.530122748277915</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>8.357924191181706</v>
+        <v>8.357924191181663</v>
       </c>
       <c r="P99" s="130" t="n">
         <v>0.5738078228343397</v>
@@ -7519,13 +7519,13 @@
         <v>71.08261052198499</v>
       </c>
       <c r="X103" s="140" t="n">
-        <v>47.14057549803177</v>
+        <v>47.14057549803176</v>
       </c>
       <c r="Y103" s="140" t="n">
         <v>0</v>
       </c>
       <c r="Z103" s="141" t="n">
-        <v>234.8920657185793</v>
+        <v>234.8920657185792</v>
       </c>
     </row>
     <row r="104" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>5758.614189381809</v>
+        <v>5758.61418938181</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>9.141959392549317</v>
@@ -9529,7 +9529,7 @@
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>2317.698464537464</v>
+        <v>2317.698464537465</v>
       </c>
       <c r="AI37" s="56" t="n">
         <v>4.864353177656564</v>
@@ -9736,7 +9736,7 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>1753.298172230914</v>
+        <v>1753.298172230913</v>
       </c>
       <c r="AI40" s="56" t="n">
         <v>4.454283009634526</v>
@@ -10280,7 +10280,7 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>5758.614189381809</v>
+        <v>5758.61418938181</v>
       </c>
       <c r="AH51" s="56" t="n">
         <v>9.940678841032806</v>
@@ -10806,10 +10806,10 @@
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>2317.698464537464</v>
+        <v>2317.698464537465</v>
       </c>
       <c r="AH57" s="56" t="n">
-        <v>6.0497311890091</v>
+        <v>6.049731189009099</v>
       </c>
     </row>
     <row r="58">
@@ -10846,7 +10846,7 @@
         <v>0</v>
       </c>
       <c r="N58" s="132" t="n">
-        <v>13.79044643211359</v>
+        <v>13.7904464321136</v>
       </c>
       <c r="P58" s="130" t="n">
         <v>10.2493426186892</v>
@@ -11077,13 +11077,13 @@
         <v>166</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>74.88002245149934</v>
+        <v>74.88002245149937</v>
       </c>
       <c r="K61" s="131" t="n">
         <v>53.80356729336189</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>33.06110095461911</v>
+        <v>33.06110095461912</v>
       </c>
       <c r="M61" s="131" t="n">
         <v>1.218010259491261</v>
@@ -11092,7 +11092,7 @@
         <v>162.9627009589716</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>75.59228217781634</v>
+        <v>75.59228217781633</v>
       </c>
       <c r="Q61" s="131" t="n">
         <v>54.62386416537736</v>
@@ -11158,19 +11158,19 @@
         <v>74</v>
       </c>
       <c r="J62" s="130" t="n">
-        <v>0.946566785750185</v>
+        <v>0.9465667857501853</v>
       </c>
       <c r="K62" s="131" t="n">
         <v>11.36424964772467</v>
       </c>
       <c r="L62" s="131" t="n">
-        <v>57.74182120542003</v>
+        <v>57.74182120542004</v>
       </c>
       <c r="M62" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N62" s="132" t="n">
-        <v>70.05263763889488</v>
+        <v>70.05263763889489</v>
       </c>
       <c r="P62" s="130" t="n">
         <v>0.9413347756941125</v>
@@ -11239,7 +11239,7 @@
         <v>8</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>0.6454387887318376</v>
+        <v>0.6454387887317949</v>
       </c>
       <c r="K63" s="131" t="n">
         <v>0.1037014274659498</v>
@@ -11251,10 +11251,10 @@
         <v>5.123650723609178</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>5.951452166512968</v>
+        <v>5.951452166512926</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>0.5738078228343113</v>
+        <v>0.5738078228343255</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>0.08753547266331907</v>
@@ -11266,7 +11266,7 @@
         <v>4.764364896346361</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>5.50495106217225</v>
+        <v>5.504951062172264</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>0.5642210685925164</v>
@@ -11575,13 +11575,13 @@
         <v>4.225076113212191</v>
       </c>
       <c r="L67" s="140" t="n">
-        <v>7.669521517167252</v>
+        <v>7.669521517167253</v>
       </c>
       <c r="M67" s="140" t="n">
         <v>0</v>
       </c>
       <c r="N67" s="141" t="n">
-        <v>30.74099485995321</v>
+        <v>30.74099485995322</v>
       </c>
       <c r="P67" s="139" t="n">
         <v>21.92887624761443</v>
@@ -11590,7 +11590,7 @@
         <v>4.655064442551426</v>
       </c>
       <c r="R67" s="140" t="n">
-        <v>6.955671695501598</v>
+        <v>6.955671695501597</v>
       </c>
       <c r="S67" s="140" t="n">
         <v>0</v>
@@ -11656,7 +11656,7 @@
         <v>69.4965944817647</v>
       </c>
       <c r="L68" s="143" t="n">
-        <v>102.3374538354153</v>
+        <v>102.3374538354154</v>
       </c>
       <c r="M68" s="143" t="n">
         <v>23.44217100622897</v>
@@ -12391,7 +12391,7 @@
         <v>0</v>
       </c>
       <c r="K79" s="131" t="n">
-        <v>0.1862264093511716</v>
+        <v>0.1862264093511717</v>
       </c>
       <c r="L79" s="131" t="n">
         <v>0</v>
@@ -12430,7 +12430,7 @@
         <v>1.7498650498326</v>
       </c>
       <c r="Z79" s="132" t="n">
-        <v>5.159103848813558</v>
+        <v>5.159103848813556</v>
       </c>
     </row>
     <row r="80">
@@ -12531,10 +12531,10 @@
         <v>0</v>
       </c>
       <c r="M81" s="131" t="n">
-        <v>2.406472024668733</v>
+        <v>2.406472024668734</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>2.406472024668733</v>
+        <v>2.406472024668734</v>
       </c>
       <c r="P81" s="130" t="n">
         <v>0</v>
@@ -12897,7 +12897,7 @@
         <v>67.28893941810735</v>
       </c>
       <c r="X86" s="143" t="n">
-        <v>43.76101560028665</v>
+        <v>43.76101560028664</v>
       </c>
       <c r="Y86" s="143" t="n">
         <v>13.47010685860509</v>
@@ -13404,7 +13404,7 @@
         <v>0</v>
       </c>
       <c r="N94" s="132" t="n">
-        <v>13.79044643211359</v>
+        <v>13.7904464321136</v>
       </c>
       <c r="P94" s="130" t="n">
         <v>10.2493426186892</v>
@@ -13593,22 +13593,22 @@
         <v>166</v>
       </c>
       <c r="J97" s="130" t="n">
-        <v>74.88002245149934</v>
+        <v>74.88002245149937</v>
       </c>
       <c r="K97" s="131" t="n">
         <v>53.98979370271307</v>
       </c>
       <c r="L97" s="131" t="n">
-        <v>33.06110095461911</v>
+        <v>33.06110095461912</v>
       </c>
       <c r="M97" s="131" t="n">
         <v>2.978503417483211</v>
       </c>
       <c r="N97" s="132" t="n">
-        <v>164.9094205263147</v>
+        <v>164.9094205263148</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>75.59228217781634</v>
+        <v>75.59228217781633</v>
       </c>
       <c r="Q97" s="131" t="n">
         <v>54.80800513548264</v>
@@ -13660,19 +13660,19 @@
         <v>74</v>
       </c>
       <c r="J98" s="130" t="n">
-        <v>0.946566785750185</v>
+        <v>0.9465667857501853</v>
       </c>
       <c r="K98" s="131" t="n">
         <v>11.36424964772467</v>
       </c>
       <c r="L98" s="131" t="n">
-        <v>57.74182120542003</v>
+        <v>57.74182120542004</v>
       </c>
       <c r="M98" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N98" s="132" t="n">
-        <v>70.05263763889488</v>
+        <v>70.05263763889489</v>
       </c>
       <c r="P98" s="130" t="n">
         <v>0.9413347756941125</v>
@@ -13727,7 +13727,7 @@
         <v>8</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>0.6454387887318376</v>
+        <v>0.6454387887317949</v>
       </c>
       <c r="K99" s="131" t="n">
         <v>0.1037014274659498</v>
@@ -13739,7 +13739,7 @@
         <v>7.530122748277915</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>8.357924191181706</v>
+        <v>8.357924191181663</v>
       </c>
       <c r="P99" s="130" t="n">
         <v>0.5738078228343397</v>
@@ -14035,13 +14035,13 @@
         <v>71.08261052198499</v>
       </c>
       <c r="X103" s="140" t="n">
-        <v>47.14057549803177</v>
+        <v>47.14057549803176</v>
       </c>
       <c r="Y103" s="140" t="n">
         <v>0</v>
       </c>
       <c r="Z103" s="141" t="n">
-        <v>234.8920657185793</v>
+        <v>234.8920657185792</v>
       </c>
     </row>
     <row r="104" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -15298,7 +15298,7 @@
         <v>8672.573012237981</v>
       </c>
       <c r="AI27" s="56" t="n">
-        <v>6.664732059646523</v>
+        <v>6.664732059646524</v>
       </c>
       <c r="AK27" s="123" t="n">
         <v>3</v>
@@ -16799,7 +16799,7 @@
         <v>6048.064903563136</v>
       </c>
       <c r="AH51" s="56" t="n">
-        <v>9.374396464881981</v>
+        <v>9.374396464881979</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" thickBot="1">
@@ -17362,7 +17362,7 @@
         <v>0</v>
       </c>
       <c r="N58" s="132" t="n">
-        <v>13.79044643211359</v>
+        <v>13.7904464321136</v>
       </c>
       <c r="P58" s="130" t="n">
         <v>10.2493426186892</v>
@@ -17593,13 +17593,13 @@
         <v>166</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>74.88002245149934</v>
+        <v>74.88002245149937</v>
       </c>
       <c r="K61" s="131" t="n">
         <v>53.80356729336189</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>33.06110095461911</v>
+        <v>33.06110095461912</v>
       </c>
       <c r="M61" s="131" t="n">
         <v>1.218010259491261</v>
@@ -17608,7 +17608,7 @@
         <v>162.9627009589716</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>75.59228217781634</v>
+        <v>75.59228217781633</v>
       </c>
       <c r="Q61" s="131" t="n">
         <v>54.62386416537736</v>
@@ -17674,19 +17674,19 @@
         <v>74</v>
       </c>
       <c r="J62" s="130" t="n">
-        <v>0.946566785750185</v>
+        <v>0.9465667857501853</v>
       </c>
       <c r="K62" s="131" t="n">
         <v>11.36424964772467</v>
       </c>
       <c r="L62" s="131" t="n">
-        <v>57.74182120542003</v>
+        <v>57.74182120542004</v>
       </c>
       <c r="M62" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N62" s="132" t="n">
-        <v>70.05263763889488</v>
+        <v>70.05263763889489</v>
       </c>
       <c r="P62" s="130" t="n">
         <v>0.9413347756941125</v>
@@ -17755,7 +17755,7 @@
         <v>8</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>0.6454387887318376</v>
+        <v>0.6454387887317949</v>
       </c>
       <c r="K63" s="131" t="n">
         <v>0.1037014274659498</v>
@@ -17767,10 +17767,10 @@
         <v>5.123650723609178</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>5.951452166512968</v>
+        <v>5.951452166512926</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>0.5738078228343113</v>
+        <v>0.5738078228343255</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>0.08753547266331907</v>
@@ -17782,7 +17782,7 @@
         <v>4.764364896346361</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>5.50495106217225</v>
+        <v>5.504951062172264</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>0.5642210685925164</v>
@@ -18091,13 +18091,13 @@
         <v>4.225076113212191</v>
       </c>
       <c r="L67" s="140" t="n">
-        <v>7.669521517167252</v>
+        <v>7.669521517167253</v>
       </c>
       <c r="M67" s="140" t="n">
         <v>0</v>
       </c>
       <c r="N67" s="141" t="n">
-        <v>30.74099485995321</v>
+        <v>30.74099485995322</v>
       </c>
       <c r="P67" s="139" t="n">
         <v>21.92887624761443</v>
@@ -18106,7 +18106,7 @@
         <v>4.655064442551426</v>
       </c>
       <c r="R67" s="140" t="n">
-        <v>6.955671695501598</v>
+        <v>6.955671695501597</v>
       </c>
       <c r="S67" s="140" t="n">
         <v>0</v>
@@ -18172,7 +18172,7 @@
         <v>69.4965944817647</v>
       </c>
       <c r="L68" s="143" t="n">
-        <v>102.3374538354153</v>
+        <v>102.3374538354154</v>
       </c>
       <c r="M68" s="143" t="n">
         <v>23.44217100622897</v>
@@ -18907,7 +18907,7 @@
         <v>0</v>
       </c>
       <c r="K79" s="131" t="n">
-        <v>0.1862264093511716</v>
+        <v>0.1862264093511717</v>
       </c>
       <c r="L79" s="131" t="n">
         <v>0</v>
@@ -18946,7 +18946,7 @@
         <v>1.7498650498326</v>
       </c>
       <c r="Z79" s="132" t="n">
-        <v>5.159103848813558</v>
+        <v>5.159103848813556</v>
       </c>
     </row>
     <row r="80">
@@ -19047,10 +19047,10 @@
         <v>0</v>
       </c>
       <c r="M81" s="131" t="n">
-        <v>2.406472024668733</v>
+        <v>2.406472024668734</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>2.406472024668733</v>
+        <v>2.406472024668734</v>
       </c>
       <c r="P81" s="130" t="n">
         <v>0</v>
@@ -19413,7 +19413,7 @@
         <v>67.28893941810735</v>
       </c>
       <c r="X86" s="143" t="n">
-        <v>43.76101560028665</v>
+        <v>43.76101560028664</v>
       </c>
       <c r="Y86" s="143" t="n">
         <v>13.47010685860509</v>
@@ -19920,7 +19920,7 @@
         <v>0</v>
       </c>
       <c r="N94" s="132" t="n">
-        <v>13.79044643211359</v>
+        <v>13.7904464321136</v>
       </c>
       <c r="P94" s="130" t="n">
         <v>10.2493426186892</v>
@@ -20109,22 +20109,22 @@
         <v>166</v>
       </c>
       <c r="J97" s="130" t="n">
-        <v>74.88002245149934</v>
+        <v>74.88002245149937</v>
       </c>
       <c r="K97" s="131" t="n">
         <v>53.98979370271307</v>
       </c>
       <c r="L97" s="131" t="n">
-        <v>33.06110095461911</v>
+        <v>33.06110095461912</v>
       </c>
       <c r="M97" s="131" t="n">
         <v>2.978503417483211</v>
       </c>
       <c r="N97" s="132" t="n">
-        <v>164.9094205263147</v>
+        <v>164.9094205263148</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>75.59228217781634</v>
+        <v>75.59228217781633</v>
       </c>
       <c r="Q97" s="131" t="n">
         <v>54.80800513548264</v>
@@ -20176,19 +20176,19 @@
         <v>74</v>
       </c>
       <c r="J98" s="130" t="n">
-        <v>0.946566785750185</v>
+        <v>0.9465667857501853</v>
       </c>
       <c r="K98" s="131" t="n">
         <v>11.36424964772467</v>
       </c>
       <c r="L98" s="131" t="n">
-        <v>57.74182120542003</v>
+        <v>57.74182120542004</v>
       </c>
       <c r="M98" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N98" s="132" t="n">
-        <v>70.05263763889488</v>
+        <v>70.05263763889489</v>
       </c>
       <c r="P98" s="130" t="n">
         <v>0.9413347756941125</v>
@@ -20243,7 +20243,7 @@
         <v>8</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>0.6454387887318376</v>
+        <v>0.6454387887317949</v>
       </c>
       <c r="K99" s="131" t="n">
         <v>0.1037014274659498</v>
@@ -20255,7 +20255,7 @@
         <v>7.530122748277915</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>8.357924191181706</v>
+        <v>8.357924191181663</v>
       </c>
       <c r="P99" s="130" t="n">
         <v>0.5738078228343397</v>
@@ -20551,13 +20551,13 @@
         <v>71.08261052198499</v>
       </c>
       <c r="X103" s="140" t="n">
-        <v>47.14057549803177</v>
+        <v>47.14057549803176</v>
       </c>
       <c r="Y103" s="140" t="n">
         <v>0</v>
       </c>
       <c r="Z103" s="141" t="n">
-        <v>234.8920657185793</v>
+        <v>234.8920657185792</v>
       </c>
     </row>
     <row r="104" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -23253,7 +23253,7 @@
         <v>87555.74838878366</v>
       </c>
       <c r="AH49" s="46" t="n">
-        <v>68.10200542396777</v>
+        <v>68.10200542396778</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" thickBot="1">
@@ -23433,10 +23433,10 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>6254.517428753081</v>
+        <v>6254.51742875308</v>
       </c>
       <c r="AH52" s="56" t="n">
-        <v>9.284039392724651</v>
+        <v>9.284039392724653</v>
       </c>
     </row>
     <row r="53">
@@ -23878,7 +23878,7 @@
         <v>0</v>
       </c>
       <c r="N58" s="132" t="n">
-        <v>13.79044643211359</v>
+        <v>13.7904464321136</v>
       </c>
       <c r="P58" s="130" t="n">
         <v>10.2493426186892</v>
@@ -24109,13 +24109,13 @@
         <v>166</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>74.88002245149934</v>
+        <v>74.88002245149937</v>
       </c>
       <c r="K61" s="131" t="n">
         <v>53.80356729336189</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>33.06110095461911</v>
+        <v>33.06110095461912</v>
       </c>
       <c r="M61" s="131" t="n">
         <v>1.218010259491261</v>
@@ -24124,7 +24124,7 @@
         <v>162.9627009589716</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>75.59228217781634</v>
+        <v>75.59228217781633</v>
       </c>
       <c r="Q61" s="131" t="n">
         <v>54.62386416537736</v>
@@ -24190,19 +24190,19 @@
         <v>74</v>
       </c>
       <c r="J62" s="130" t="n">
-        <v>0.946566785750185</v>
+        <v>0.9465667857501853</v>
       </c>
       <c r="K62" s="131" t="n">
         <v>11.36424964772467</v>
       </c>
       <c r="L62" s="131" t="n">
-        <v>57.74182120542003</v>
+        <v>57.74182120542004</v>
       </c>
       <c r="M62" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N62" s="132" t="n">
-        <v>70.05263763889488</v>
+        <v>70.05263763889489</v>
       </c>
       <c r="P62" s="130" t="n">
         <v>0.9413347756941125</v>
@@ -24271,7 +24271,7 @@
         <v>8</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>0.6454387887318376</v>
+        <v>0.6454387887317949</v>
       </c>
       <c r="K63" s="131" t="n">
         <v>0.1037014274659498</v>
@@ -24283,10 +24283,10 @@
         <v>5.123650723609178</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>5.951452166512968</v>
+        <v>5.951452166512926</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>0.5738078228343113</v>
+        <v>0.5738078228343255</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>0.08753547266331907</v>
@@ -24298,7 +24298,7 @@
         <v>4.764364896346361</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>5.50495106217225</v>
+        <v>5.504951062172264</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>0.5642210685925164</v>
@@ -24598,13 +24598,13 @@
         <v>4.225076113212191</v>
       </c>
       <c r="L67" s="140" t="n">
-        <v>7.669521517167252</v>
+        <v>7.669521517167253</v>
       </c>
       <c r="M67" s="140" t="n">
         <v>0</v>
       </c>
       <c r="N67" s="141" t="n">
-        <v>30.74099485995321</v>
+        <v>30.74099485995322</v>
       </c>
       <c r="P67" s="139" t="n">
         <v>21.92887624761443</v>
@@ -24613,7 +24613,7 @@
         <v>4.655064442551426</v>
       </c>
       <c r="R67" s="140" t="n">
-        <v>6.955671695501598</v>
+        <v>6.955671695501597</v>
       </c>
       <c r="S67" s="140" t="n">
         <v>0</v>
@@ -24670,7 +24670,7 @@
         <v>69.4965944817647</v>
       </c>
       <c r="L68" s="143" t="n">
-        <v>102.3374538354153</v>
+        <v>102.3374538354154</v>
       </c>
       <c r="M68" s="143" t="n">
         <v>23.44217100622897</v>
@@ -25413,7 +25413,7 @@
         <v>0</v>
       </c>
       <c r="K79" s="131" t="n">
-        <v>0.1862264093511716</v>
+        <v>0.1862264093511717</v>
       </c>
       <c r="L79" s="131" t="n">
         <v>0</v>
@@ -25452,7 +25452,7 @@
         <v>1.7498650498326</v>
       </c>
       <c r="Z79" s="132" t="n">
-        <v>5.159103848813558</v>
+        <v>5.159103848813556</v>
       </c>
     </row>
     <row r="80">
@@ -25553,10 +25553,10 @@
         <v>0</v>
       </c>
       <c r="M81" s="131" t="n">
-        <v>2.406472024668733</v>
+        <v>2.406472024668734</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>2.406472024668733</v>
+        <v>2.406472024668734</v>
       </c>
       <c r="P81" s="130" t="n">
         <v>0</v>
@@ -25919,7 +25919,7 @@
         <v>67.28893941810735</v>
       </c>
       <c r="X86" s="143" t="n">
-        <v>43.76101560028665</v>
+        <v>43.76101560028664</v>
       </c>
       <c r="Y86" s="143" t="n">
         <v>13.47010685860509</v>
@@ -26426,7 +26426,7 @@
         <v>0</v>
       </c>
       <c r="N94" s="132" t="n">
-        <v>13.79044643211359</v>
+        <v>13.7904464321136</v>
       </c>
       <c r="P94" s="130" t="n">
         <v>10.2493426186892</v>
@@ -26615,22 +26615,22 @@
         <v>166</v>
       </c>
       <c r="J97" s="130" t="n">
-        <v>74.88002245149934</v>
+        <v>74.88002245149937</v>
       </c>
       <c r="K97" s="131" t="n">
         <v>53.98979370271307</v>
       </c>
       <c r="L97" s="131" t="n">
-        <v>33.06110095461911</v>
+        <v>33.06110095461912</v>
       </c>
       <c r="M97" s="131" t="n">
         <v>2.978503417483211</v>
       </c>
       <c r="N97" s="132" t="n">
-        <v>164.9094205263147</v>
+        <v>164.9094205263148</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>75.59228217781634</v>
+        <v>75.59228217781633</v>
       </c>
       <c r="Q97" s="131" t="n">
         <v>54.80800513548264</v>
@@ -26682,19 +26682,19 @@
         <v>74</v>
       </c>
       <c r="J98" s="130" t="n">
-        <v>0.946566785750185</v>
+        <v>0.9465667857501853</v>
       </c>
       <c r="K98" s="131" t="n">
         <v>11.36424964772467</v>
       </c>
       <c r="L98" s="131" t="n">
-        <v>57.74182120542003</v>
+        <v>57.74182120542004</v>
       </c>
       <c r="M98" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N98" s="132" t="n">
-        <v>70.05263763889488</v>
+        <v>70.05263763889489</v>
       </c>
       <c r="P98" s="130" t="n">
         <v>0.9413347756941125</v>
@@ -26749,7 +26749,7 @@
         <v>8</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>0.6454387887318376</v>
+        <v>0.6454387887317949</v>
       </c>
       <c r="K99" s="131" t="n">
         <v>0.1037014274659498</v>
@@ -26761,7 +26761,7 @@
         <v>7.530122748277915</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>8.357924191181706</v>
+        <v>8.357924191181663</v>
       </c>
       <c r="P99" s="130" t="n">
         <v>0.5738078228343397</v>
@@ -27057,13 +27057,13 @@
         <v>71.08261052198499</v>
       </c>
       <c r="X103" s="140" t="n">
-        <v>47.14057549803177</v>
+        <v>47.14057549803176</v>
       </c>
       <c r="Y103" s="140" t="n">
         <v>0</v>
       </c>
       <c r="Z103" s="141" t="n">
-        <v>234.8920657185793</v>
+        <v>234.8920657185792</v>
       </c>
     </row>
     <row r="104" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -28166,7 +28166,7 @@
         <v>97701.03174199554</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>73.90391183428737</v>
+        <v>73.90391183428736</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -28611,7 +28611,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>6531.668755170008</v>
+        <v>6531.668755170009</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>9.087539887934609</v>
@@ -29925,7 +29925,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>6531.668755170009</v>
+        <v>6531.668755170008</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>9.254144785880076</v>
@@ -30370,7 +30370,7 @@
         <v>0</v>
       </c>
       <c r="N58" s="132" t="n">
-        <v>13.79044643211359</v>
+        <v>13.7904464321136</v>
       </c>
       <c r="P58" s="130" t="n">
         <v>10.2493426186892</v>
@@ -30601,13 +30601,13 @@
         <v>166</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>74.88002245149934</v>
+        <v>74.88002245149937</v>
       </c>
       <c r="K61" s="131" t="n">
         <v>53.80356729336189</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>33.06110095461911</v>
+        <v>33.06110095461912</v>
       </c>
       <c r="M61" s="131" t="n">
         <v>1.218010259491261</v>
@@ -30616,7 +30616,7 @@
         <v>162.9627009589716</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>75.59228217781634</v>
+        <v>75.59228217781633</v>
       </c>
       <c r="Q61" s="131" t="n">
         <v>54.62386416537736</v>
@@ -30682,19 +30682,19 @@
         <v>74</v>
       </c>
       <c r="J62" s="130" t="n">
-        <v>0.946566785750185</v>
+        <v>0.9465667857501853</v>
       </c>
       <c r="K62" s="131" t="n">
         <v>11.36424964772467</v>
       </c>
       <c r="L62" s="131" t="n">
-        <v>57.74182120542003</v>
+        <v>57.74182120542004</v>
       </c>
       <c r="M62" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N62" s="132" t="n">
-        <v>70.05263763889488</v>
+        <v>70.05263763889489</v>
       </c>
       <c r="P62" s="130" t="n">
         <v>0.9413347756941125</v>
@@ -30754,7 +30754,7 @@
         <v>8</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>0.6454387887318376</v>
+        <v>0.6454387887317949</v>
       </c>
       <c r="K63" s="131" t="n">
         <v>0.1037014274659498</v>
@@ -30766,10 +30766,10 @@
         <v>5.123650723609178</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>5.951452166512968</v>
+        <v>5.951452166512926</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>0.5738078228343113</v>
+        <v>0.5738078228343255</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>0.08753547266331907</v>
@@ -30781,7 +30781,7 @@
         <v>4.764364896346361</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>5.50495106217225</v>
+        <v>5.504951062172264</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>0.5642210685925164</v>
@@ -31072,13 +31072,13 @@
         <v>4.225076113212191</v>
       </c>
       <c r="L67" s="140" t="n">
-        <v>7.669521517167252</v>
+        <v>7.669521517167253</v>
       </c>
       <c r="M67" s="140" t="n">
         <v>0</v>
       </c>
       <c r="N67" s="141" t="n">
-        <v>30.74099485995321</v>
+        <v>30.74099485995322</v>
       </c>
       <c r="P67" s="139" t="n">
         <v>21.92887624761443</v>
@@ -31087,7 +31087,7 @@
         <v>4.655064442551426</v>
       </c>
       <c r="R67" s="140" t="n">
-        <v>6.955671695501598</v>
+        <v>6.955671695501597</v>
       </c>
       <c r="S67" s="140" t="n">
         <v>0</v>
@@ -31153,7 +31153,7 @@
         <v>69.4965944817647</v>
       </c>
       <c r="L68" s="143" t="n">
-        <v>102.3374538354153</v>
+        <v>102.3374538354154</v>
       </c>
       <c r="M68" s="143" t="n">
         <v>23.44217100622897</v>
@@ -31896,7 +31896,7 @@
         <v>0</v>
       </c>
       <c r="K79" s="131" t="n">
-        <v>0.1862264093511716</v>
+        <v>0.1862264093511717</v>
       </c>
       <c r="L79" s="131" t="n">
         <v>0</v>
@@ -31935,7 +31935,7 @@
         <v>1.7498650498326</v>
       </c>
       <c r="Z79" s="132" t="n">
-        <v>5.159103848813558</v>
+        <v>5.159103848813556</v>
       </c>
     </row>
     <row r="80">
@@ -32036,10 +32036,10 @@
         <v>0</v>
       </c>
       <c r="M81" s="131" t="n">
-        <v>2.406472024668733</v>
+        <v>2.406472024668734</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>2.406472024668733</v>
+        <v>2.406472024668734</v>
       </c>
       <c r="P81" s="130" t="n">
         <v>0</v>
@@ -32402,7 +32402,7 @@
         <v>67.28893941810735</v>
       </c>
       <c r="X86" s="143" t="n">
-        <v>43.76101560028665</v>
+        <v>43.76101560028664</v>
       </c>
       <c r="Y86" s="143" t="n">
         <v>13.47010685860509</v>
@@ -32909,7 +32909,7 @@
         <v>0</v>
       </c>
       <c r="N94" s="132" t="n">
-        <v>13.79044643211359</v>
+        <v>13.7904464321136</v>
       </c>
       <c r="P94" s="130" t="n">
         <v>10.2493426186892</v>
@@ -33098,22 +33098,22 @@
         <v>166</v>
       </c>
       <c r="J97" s="130" t="n">
-        <v>74.88002245149934</v>
+        <v>74.88002245149937</v>
       </c>
       <c r="K97" s="131" t="n">
         <v>53.98979370271307</v>
       </c>
       <c r="L97" s="131" t="n">
-        <v>33.06110095461911</v>
+        <v>33.06110095461912</v>
       </c>
       <c r="M97" s="131" t="n">
         <v>2.978503417483211</v>
       </c>
       <c r="N97" s="132" t="n">
-        <v>164.9094205263147</v>
+        <v>164.9094205263148</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>75.59228217781634</v>
+        <v>75.59228217781633</v>
       </c>
       <c r="Q97" s="131" t="n">
         <v>54.80800513548264</v>
@@ -33165,19 +33165,19 @@
         <v>74</v>
       </c>
       <c r="J98" s="130" t="n">
-        <v>0.946566785750185</v>
+        <v>0.9465667857501853</v>
       </c>
       <c r="K98" s="131" t="n">
         <v>11.36424964772467</v>
       </c>
       <c r="L98" s="131" t="n">
-        <v>57.74182120542003</v>
+        <v>57.74182120542004</v>
       </c>
       <c r="M98" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N98" s="132" t="n">
-        <v>70.05263763889488</v>
+        <v>70.05263763889489</v>
       </c>
       <c r="P98" s="130" t="n">
         <v>0.9413347756941125</v>
@@ -33232,7 +33232,7 @@
         <v>8</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>0.6454387887318376</v>
+        <v>0.6454387887317949</v>
       </c>
       <c r="K99" s="131" t="n">
         <v>0.1037014274659498</v>
@@ -33244,7 +33244,7 @@
         <v>7.530122748277915</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>8.357924191181706</v>
+        <v>8.357924191181663</v>
       </c>
       <c r="P99" s="130" t="n">
         <v>0.5738078228343397</v>
@@ -33540,13 +33540,13 @@
         <v>71.08261052198499</v>
       </c>
       <c r="X103" s="140" t="n">
-        <v>47.14057549803177</v>
+        <v>47.14057549803176</v>
       </c>
       <c r="Y103" s="140" t="n">
         <v>0</v>
       </c>
       <c r="Z103" s="141" t="n">
-        <v>234.8920657185793</v>
+        <v>234.8920657185792</v>
       </c>
     </row>
     <row r="104" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
